--- a/engineering/ag-research/final-results.xlsx
+++ b/engineering/ag-research/final-results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/flannerymcnair/Documents/GitHub/resume-website/engineering/ag-research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8697AF4E-D59C-1D49-9CE4-A8ECF9F3D3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDF25D9-0171-654A-A9E8-5F5306146E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="concentration" sheetId="1" r:id="rId1"/>
@@ -268,35 +268,69 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="757575"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>percent V vs. organ</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Pecent Vanadium per Plant Organ</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -319,17 +353,124 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4285F4"/>
-            </a:solidFill>
-            <a:ln cmpd="sng">
+          <c:invertIfNegative val="1"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="1"/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>concentration!$H$18:$H$20</c:f>
@@ -366,34 +507,21 @@
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:ln cmpd="sng">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                  </a:ln>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-0E12-C249-85C2-E7FD0DB91AF5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="65"/>
         <c:axId val="271651647"/>
         <c:axId val="2067646754"/>
       </c:barChart>
@@ -407,45 +535,90 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>organ</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Organ</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -463,106 +636,150 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
-              </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
+                      <a:alpha val="42000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                      <a:alpha val="36000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t>percent V</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Vanadium (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="271651647"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0">
-            <a:defRPr b="0">
-              <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -571,16 +788,626 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>136525</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3848100" cy="2371725"/>
+    <xdr:ext cx="6896100" cy="4321175"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1" title="Chart">
